--- a/AAII_Financials/Yearly/HTHIY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/HTHIY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>HTHIY</t>
   </si>
@@ -656,223 +656,235 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42825</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42460</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42094</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41729</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41364</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40999</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>66581400</v>
+      </c>
+      <c r="E8" s="3">
         <v>65332200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>64320000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>81853800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>84528200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>78926500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>81478600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>85557400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>88212600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>61753700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>73752100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>83380200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>88544600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>82183300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>87379600</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>46585000</v>
+      </c>
+      <c r="E9" s="3">
         <v>46495000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>47248900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>61625000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>63458200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>59077300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>59449600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>62852000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>64653500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>45715200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>54824200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>61400900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>65711500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>61302900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>65801900</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>19996400</v>
+      </c>
+      <c r="E10" s="3">
         <v>18837300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>17071100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>20228700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>21070100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19849200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>22029000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>22705400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>23559100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>16038400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>18928000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>21979200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>22833100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>20880500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>21577700</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -891,37 +903,38 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1825700</v>
+      </c>
+      <c r="E12" s="3">
         <v>1732200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1918000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>2378600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>2613600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>2654400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>2730400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>2916200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3134700</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -929,18 +942,21 @@
       <c r="N12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O12" s="3">
+      <c r="O12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P12" s="3">
         <v>3219100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3102500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3729100</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,87 +1002,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1101500</v>
+      </c>
+      <c r="E14" s="3">
         <v>560700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>211900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1030100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-630600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-3026700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4359500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1509000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>672500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>125500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>357800</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>568700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>488200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>496600</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2880200</v>
+      </c>
+      <c r="E15" s="3">
         <v>2881700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2985200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>3959200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>3070300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3018400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2744800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2724200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2778600</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1082,9 +1104,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1100,104 +1125,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>58360700</v>
+      </c>
+      <c r="E17" s="3">
         <v>58906700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>58982400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>74765600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>78448900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>74449300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>75327400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>78744200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>81483800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>57920600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>69443600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>77909700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>83004700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>78835300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>84149200</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8220700</v>
+      </c>
+      <c r="E18" s="3">
         <v>6425600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5337600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7088100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6079300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4477300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6151200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>6813200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>6728800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>3833000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4308500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>5470500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>5539900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>3348000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>3230400</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1216,248 +1248,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-474800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-647000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-481200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-244000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-244400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-152900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>136700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>721200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>48700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-543200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-317300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-808100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1160800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>26600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2065900</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11575800</v>
+      </c>
+      <c r="E21" s="3">
         <v>9954300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>8804000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11291300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9394100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7648600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>8759300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>8816200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9458600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>6100600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7688000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8813600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12044900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7182800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>9637300</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>211600</v>
+      </c>
+      <c r="E22" s="3">
         <v>313300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>468900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>386000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>223200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>206000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>222900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>185200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>193400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>128200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>191000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>235400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>485700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>242800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>254400</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>8006700</v>
+      </c>
+      <c r="E23" s="3">
         <v>6429000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5459700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6168300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>6911800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7635200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1675300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4661100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6013300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3161700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3800200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4427000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>6215000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3131800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>5041900</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2652000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2042600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1316000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>873400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1387300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2940800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>476300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1681700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1240100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>843300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1214300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1041300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1342300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>971000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>1310100</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1503,105 +1551,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5354700</v>
+      </c>
+      <c r="E26" s="3">
         <v>4386500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4143700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5294900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5524500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4694400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1199100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2979500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4773200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2318400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2586000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3385700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4872700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>2160900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3731800</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5046200</v>
+      </c>
+      <c r="E27" s="3">
         <v>4111700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3900000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4883100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>4804800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4535400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>814100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2008400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3417800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1598800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1684900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2311500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2947500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1593700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>3138500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1647,9 +1704,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1666,38 +1726,41 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>-6200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-16500</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-82400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-150800</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-40100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-419500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-456400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-63700</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1743,9 +1806,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1791,105 +1857,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>474800</v>
+      </c>
+      <c r="E32" s="3">
         <v>647000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>481200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>244000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>244400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>152900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-136700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-721200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-48700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>543200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>317300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>808100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1160800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-26600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2065900</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5046200</v>
+      </c>
+      <c r="E33" s="3">
         <v>4111700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3900000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4883100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>4804800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4535400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>814100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2008400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3417800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1558700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1265300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1855100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2883800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1593700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>3138500</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1935,110 +2010,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5046200</v>
+      </c>
+      <c r="E35" s="3">
         <v>4111700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3900000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4883100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>4804800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4535400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>814100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2008400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3417800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1558700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1265300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1855100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2883800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1593700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>3138500</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42825</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42460</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42094</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41729</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41364</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40999</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2057,8 +2141,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2077,85 +2162,89 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8323500</v>
+      </c>
+      <c r="E41" s="3">
         <v>5784700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4663400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6268400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7978200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9185300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7549400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7288100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6571900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5157700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5140000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5985500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>10248900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>4796200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5601000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>2234500</v>
+      </c>
+      <c r="E42" s="3">
         <v>2126400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>2190200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2609700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3098900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2967100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>2601700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2565400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>3420800</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>8</v>
@@ -2163,354 +2252,378 @@
       <c r="N42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O42" s="3">
+      <c r="O42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P42" s="3">
         <v>562300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>307300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>882600</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25187200</v>
+      </c>
+      <c r="E43" s="3">
         <v>23348200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>19776600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>21627200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24524800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>24724200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>21005200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>21658100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>23647000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>16685000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>24486700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>27359100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>52145700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>22013900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>21185000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>11134700</v>
+      </c>
+      <c r="E44" s="3">
         <v>10459500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9987400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>12383500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16819300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14949500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>13094000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12244000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12948800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8262600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>9553900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12437800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>25153900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13066000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>12775800</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2597900</v>
+      </c>
+      <c r="E45" s="3">
         <v>2341000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2089100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1708800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1924600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1911300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4239400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1689700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1919600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3612300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3982600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>4394600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12337400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6995000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6221800</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>49477900</v>
+      </c>
+      <c r="E46" s="3">
         <v>44059600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>38706800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>44597600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>54345800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>53737400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>48489700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>45445300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>48508100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>33717600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>43163300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>50177000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>48200700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>47178400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>46666200</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9157700</v>
+      </c>
+      <c r="E47" s="3">
         <v>9189400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8654800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8957900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8202000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>8966300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8354600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10753100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>13049200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9770300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20098000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>18180500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>30201500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8302500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8587100</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>10395400</v>
+      </c>
+      <c r="E48" s="3">
         <v>8958600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8078000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12791800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20413600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>21780400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>20123300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>17658000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20006800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>13469300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>18376700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21090400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>42145400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20724900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>18310900</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>24296300</v>
+      </c>
+      <c r="E49" s="3">
         <v>24620200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>23473100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>25652100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>28088000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19223000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10369000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>8663600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9927700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6195400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7867500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7963500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>13682500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>6412000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5514100</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2556,9 +2669,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2604,9 +2720,12 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2619,42 +2738,45 @@
       <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3">
         <v>2256200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2035000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1671800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1583600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1271000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1982200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2744500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8648400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>16096700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6548200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6065300</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2700,57 +2822,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>94596100</v>
+      </c>
+      <c r="E54" s="3">
         <v>88714500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>80799200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>94042300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>114362600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>107169600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>92285300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>86874800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>95161300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>65134800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>92249900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>106060000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>101659000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>89165900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>85143500</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2769,8 +2897,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2789,56 +2918,60 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>10432100</v>
+      </c>
+      <c r="E57" s="3">
         <v>10502700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>9253900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11648600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>14449300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13706800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>11809000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12688500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14471900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>9451100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10671600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>12168200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>24708200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11224900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11767900</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2846,239 +2979,254 @@
         <v>2951400</v>
       </c>
       <c r="E58" s="3">
+        <v>2951400</v>
+      </c>
+      <c r="F58" s="3">
         <v>1489600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6917000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12933300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6248000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3852500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2673800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2246900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2605600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11193600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12464200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>22701800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8730300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>9370700</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26664400</v>
+      </c>
+      <c r="E59" s="3">
         <v>21081000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16396900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>14873600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>14747600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15293000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13415700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11276900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12453200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13021900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>14842300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16136500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>31285500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16078800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16023700</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>45074900</v>
+      </c>
+      <c r="E60" s="3">
         <v>39451900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>31751700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>38862700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>48207800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>41563900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34694300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>32538200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>35736500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>25078600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>36707500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>40768900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>39392100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>36034000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>37162300</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3394600</v>
+      </c>
+      <c r="E61" s="3">
         <v>5102900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6311900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>9732900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12815000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15428100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>9948700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6393700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7642400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5324700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15299200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>18882600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>16641500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12813700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12510400</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1710700</v>
+      </c>
+      <c r="E62" s="3">
         <v>1546600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1626500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1710500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4396600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>4748300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>2765800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>2954000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3399500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7117800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>9920300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>9760400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>21289400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11418500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10393900</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3124,9 +3272,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3172,9 +3323,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3220,57 +3374,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>52002400</v>
+      </c>
+      <c r="E66" s="3">
         <v>48437300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>42059300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>53905300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>70262200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>66859700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52632300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47037200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52680500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>45136600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>72147100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>80962000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>77214500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>70235400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>69126600</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3289,8 +3449,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3336,9 +3497,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3384,9 +3548,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3432,9 +3599,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3480,57 +3650,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>29934700</v>
+      </c>
+      <c r="E72" s="3">
         <v>29052200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>27005600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>27360800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>26333000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>24508400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>21339800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20644200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>19823900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12088700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11831700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12603200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>26246700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12459900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11228700</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3576,9 +3752,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3624,9 +3803,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3672,57 +3854,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41309200</v>
+      </c>
+      <c r="E76" s="3">
         <v>39046200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>37709200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>37182800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>35754700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31876400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>29367400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>29443200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>30865100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19998200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>20102800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>25097700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>24444900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>18930500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>16016900</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3768,110 +3956,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42825</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42460</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42094</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41729</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41364</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40999</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5046200</v>
+      </c>
+      <c r="E81" s="3">
         <v>4111700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3900000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4883100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>4804800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4535400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>814100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2008400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3417800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1558700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1265300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1855100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2883800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1593700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>3138500</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3890,56 +4087,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2880200</v>
+      </c>
+      <c r="E83" s="3">
         <v>2881700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2985200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>3959200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3153300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3121200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3182600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2451800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2499100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2798300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3732300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>4103100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>5321000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3799800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>4336200</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3985,9 +4186,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4033,9 +4237,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4081,9 +4288,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4129,9 +4339,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4177,57 +4390,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10490600</v>
+      </c>
+      <c r="E89" s="3">
         <v>7828100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6324500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6221500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6011000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7171200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5212900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5505100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6846800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4243400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5969900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3854100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2810100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5304100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>4042300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4246,56 +4465,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2212400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1648400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1539600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2445500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2303400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3000800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3450500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3314800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4105100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6680500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6844200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15077100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6520900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5485900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4341,9 +4564,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4389,57 +4615,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2148100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3830800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-869700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>1136400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8637300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4148700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4886800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1469800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4466200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2277800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5371400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5225000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5039600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5030900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1768100</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4458,56 +4690,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1288700</v>
+      </c>
+      <c r="E96" s="3">
         <v>1262500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>954300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>970400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>915300</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>873500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>852200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>696600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>636200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-390500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-425600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-472900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-441500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-423300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-244200</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4553,9 +4789,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4601,9 +4840,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4649,151 +4891,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-6107000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-2832200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-6776000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-8598000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1669500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1671200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>26400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2891700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-3026700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1412300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-194500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1989200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2096200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1640200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-1517300</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>640000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-90800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>475500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>220500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>569200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>489200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-308500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-154300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>12600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-108900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-421500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>584800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>475100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>531300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-171500</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2875600</v>
+      </c>
+      <c r="E102" s="3">
         <v>1074300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-845700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1019600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-387500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1840500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>44000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>989300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-633500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>444300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1203100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>341700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-835800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>585500</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
